--- a/Korean/Images.xlsx
+++ b/Korean/Images.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SteamLibrary\steamapps\common\Road to Vostok\mods\Trans To Vostok\Korean\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F91F4969-F7CE-46DE-BFE7-8F9ED78DDB8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB7A4BFB-A16D-4739-8204-30FB913F25B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{E0CAA4CC-5EC0-4298-9780-F39DB2CE6684}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="75">
   <si>
     <t>Tutorial</t>
   </si>
@@ -100,6 +100,10 @@
   </si>
   <si>
     <t>2. Interface</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TX_Tutorial_Interface.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1049,7 +1053,7 @@
         <v>4</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>12</v>
@@ -1069,16 +1073,16 @@
         <v>14</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>12</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="261">
@@ -1089,19 +1093,19 @@
         <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>12</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="243.6">
@@ -1112,19 +1116,19 @@
         <v>3</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>12</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="261">
@@ -1135,19 +1139,19 @@
         <v>3</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="278.39999999999998">
@@ -1158,19 +1162,19 @@
         <v>3</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="313.2">
@@ -1181,19 +1185,19 @@
         <v>3</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="261">
@@ -1204,19 +1208,19 @@
         <v>3</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="261">
@@ -1227,19 +1231,19 @@
         <v>3</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="400.2">
@@ -1250,19 +1254,19 @@
         <v>3</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="261">
@@ -1273,19 +1277,19 @@
         <v>3</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="261">
@@ -1296,19 +1300,19 @@
         <v>3</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="261">
@@ -1319,19 +1323,19 @@
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F14" t="s">
         <v>11</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="278.39999999999998">
@@ -1342,19 +1346,19 @@
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F15" t="s">
         <v>11</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="243.6">
@@ -1365,19 +1369,19 @@
         <v>2</v>
       </c>
       <c r="C16" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="E16" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="261">
@@ -1388,19 +1392,19 @@
         <v>2</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F17" t="s">
         <v>11</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
